--- a/notebooks/prediction/planning_journalier.xlsx
+++ b/notebooks/prediction/planning_journalier.xlsx
@@ -494,7 +494,7 @@
         <v>45292</v>
       </c>
       <c r="B2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2" t="n">
         <v>6</v>
@@ -525,12 +525,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>⚠️ Système saturé — renfort nécessaire</t>
+          <t>🟢 Activité faible</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>⚠️ Système saturé — renfort nécessaire</t>
+          <t>👍 Ajouter 1 médecin améliore la qualité</t>
         </is>
       </c>
     </row>
@@ -545,7 +545,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
         <v>5</v>
@@ -565,7 +565,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>🟡 Activité normale</t>
+          <t>⚠️ Système saturé — renfort nécessaire</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -590,7 +590,7 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E4" t="n">
         <v>5</v>
@@ -600,7 +600,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>👍 Ajouter 1 médecin améliore la qualité</t>
+          <t>🟡 Activité normale</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -635,7 +635,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E5" t="n">
         <v>5</v>
@@ -655,7 +655,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>🟡 Activité normale</t>
+          <t>⚠️ Système saturé — renfort nécessaire</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>⚠️ Système saturé — renfort nécessaire</t>
+          <t>👍 Ajouter 1 médecin améliore la qualité</t>
         </is>
       </c>
     </row>
@@ -705,7 +705,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>👍 Ajouter 1 médecin améliore la qualité</t>
+          <t>🟢 Activité faible</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -731,7 +731,7 @@
         <v>5</v>
       </c>
       <c r="F7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>👍 Ajouter 1 médecin améliore la qualité</t>
+          <t>⚠️ Système saturé — renfort nécessaire</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -830,12 +830,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>🟡 Activité normale</t>
+          <t>👍 Ajouter 1 médecin améliore la qualité</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>🟡 Activité normale</t>
+          <t>⚠️ Système saturé — renfort nécessaire</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>👍 Ajouter 1 médecin améliore la qualité</t>
+          <t>⚠️ Système saturé — renfort nécessaire</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -885,12 +885,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>👍 Ajouter 1 médecin améliore la qualité</t>
+          <t>⚠️ Système saturé — renfort nécessaire</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>👍 Ajouter 1 médecin améliore la qualité</t>
+          <t>⚠️ Système saturé — renfort nécessaire</t>
         </is>
       </c>
     </row>
@@ -1046,7 +1046,7 @@
         <v>5</v>
       </c>
       <c r="F14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>👍 Ajouter 1 médecin améliore la qualité</t>
+          <t>⚠️ Système saturé — renfort nécessaire</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>🟡 Activité normale</t>
+          <t>⚠️ Système saturé — renfort nécessaire</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>👍 Ajouter 1 médecin améliore la qualité</t>
+          <t>⚠️ Système saturé — renfort nécessaire</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>🟡 Activité normale</t>
+          <t>👍 Ajouter 1 médecin améliore la qualité</t>
         </is>
       </c>
     </row>
@@ -1217,7 +1217,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D18" t="n">
         <v>6</v>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>👍 Ajouter 1 médecin améliore la qualité</t>
+          <t>🟡 Activité normale</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>🟡 Activité normale</t>
+          <t>⚠️ Système saturé — renfort nécessaire</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>🟡 Activité normale</t>
+          <t>⚠️ Système saturé — renfort nécessaire</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>🟡 Activité normale</t>
+          <t>⚠️ Système saturé — renfort nécessaire</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>👍 Ajouter 1 médecin améliore la qualité</t>
+          <t>🟢 Activité faible</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2306,7 +2306,7 @@
         <v>5</v>
       </c>
       <c r="F42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2370,7 +2370,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>⚠️ Système saturé — renfort nécessaire</t>
+          <t>👍 Ajouter 1 médecin améliore la qualité</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>⚠️ Système saturé — renfort nécessaire</t>
+          <t>🔴 Forte activité</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>🟡 Activité normale</t>
+          <t>👍 Ajouter 1 médecin améliore la qualité</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2792,7 @@
         <v>6</v>
       </c>
       <c r="C53" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D53" t="n">
         <v>6</v>
@@ -2810,7 +2810,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>👍 Ajouter 1 médecin améliore la qualité</t>
+          <t>🟡 Activité normale</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2825,7 +2825,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>🟡 Activité normale</t>
+          <t>👍 Ajouter 1 médecin améliore la qualité</t>
         </is>
       </c>
     </row>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>👍 Ajouter 1 médecin améliore la qualité</t>
+          <t>⚠️ Système saturé — renfort nécessaire</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>⚠️ Système saturé — renfort nécessaire</t>
+          <t>👍 Ajouter 1 médecin améliore la qualité</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>👍 Ajouter 1 médecin améliore la qualité</t>
+          <t>⚠️ Système saturé — renfort nécessaire</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>👍 Ajouter 1 médecin améliore la qualité</t>
+          <t>⚠️ Système saturé — renfort nécessaire</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>🟡 Activité normale</t>
+          <t>👍 Ajouter 1 médecin améliore la qualité</t>
         </is>
       </c>
     </row>
@@ -4155,7 +4155,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>🔴 Forte activité</t>
+          <t>⚠️ Système saturé — renfort nécessaire</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4286,11 +4286,11 @@
         <v>6</v>
       </c>
       <c r="F86" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>⚠️ Système saturé — renfort nécessaire</t>
+          <t>🔴 Forte activité</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -4390,7 +4390,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>🟡 Activité normale</t>
+          <t>⚠️ Système saturé — renfort nécessaire</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -4435,7 +4435,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>🟡 Activité normale</t>
+          <t>⚠️ Système saturé — renfort nécessaire</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
